--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-02-2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£10.57</t>
+          <t>£10.33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£15.27</t>
+          <t>£15.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.26</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£15.86</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£19.78</t>
+          <t>£19.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£22.06</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.06</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£22.13</t>
+          <t>£22.10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.11</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£25.48</t>
+          <t>£25.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£25.47</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1274,14 +1274,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/90mm-celotex-ga3090-2-4m-x-1-2m</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>£27.67</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£27.67</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>£28.25</t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>£27.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£27.20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£33.14</t>
+          <t>£32.98</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£33.38</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£40.77</t>
+          <t>£39.40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£40.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£39.44</t>
+          <t>£39.41</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£41.19</t>
+          <t>£39.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£42.35</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£40.68</t>
+          <t>£40.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£40.68</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£752.82</t>
+          <t>£744.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£779.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£945.08</t>
+          <t>£934.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1019.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£28.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-pl4000-thermal-laminate-insulation-board?variant=55597627507072</t>
+          <t>£40.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£43.46</t>
+          <t>£44.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£48.17</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>£44.81</t>
+          <t>£44.16</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£47.58</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>£43.69</t>
+          <t>£43.59</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£1,016.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£47.08</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1206.88</t>
+          <t>£1201.6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1267.2</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1353.92</t>
+          <t>£1337.92</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1283.2</t>
+          <t>£1276.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
